--- a/docs/pension_data_combined_2026-09-24.xlsx
+++ b/docs/pension_data_combined_2026-09-24.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.1724</v>
-      </c>
       <c r="D48" t="n">
         <v>4198981.4</v>
       </c>
